--- a/docs/GRANKHA_Margenes_IVA_Envios.xlsx
+++ b/docs/GRANKHA_Margenes_IVA_Envios.xlsx
@@ -553,15 +553,15 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Coste de envío del proveedor por pedido</t>
+          <t>Coste de envío del proveedor (tarifa real AW, por pedido)</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>5</v>
+        <v>2.95</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ajusta con la tarifa real de AW Dropshipping (varía por peso y destino).</t>
+          <t>VERIFICADO en aw-dropship.es/shipping (15/10/2026): 2,95 € hasta 1 kg · 4,00 € de 1 a 5 kg · 6,50 € más de 5 kg. Sin IVA (deducible).</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P47"/>
+  <dimension ref="A1:P53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -826,7 +826,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>XS (2-4 kg) · Rosa suave · Colgante de cuarzo rosa</t>
+          <t>XS (2-4 kg) · Rosa suave · Cuarzo rosa</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>18.63</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>37.25</v>
+        <v>36.9</v>
       </c>
       <c r="H5" s="9">
         <f>G5-G5/(1+Supuestos!$B$5)</f>
@@ -893,7 +893,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>XS (2-4 kg) · Lavanda · Colgante de amatista</t>
+          <t>XS (2-4 kg) · Lavanda · Amatista</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -902,13 +902,13 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>18.63</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>37.25</v>
+        <v>36.9</v>
       </c>
       <c r="H6" s="9">
         <f>G6-G6/(1+Supuestos!$B$5)</f>
@@ -960,7 +960,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>XS (2-4 kg) · Rock Grey · Colgante de obsidiana negra</t>
+          <t>XS (2-4 kg) · Rock Grey · Obsidiana negra</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -969,13 +969,13 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>18.63</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>37.25</v>
+        <v>36.9</v>
       </c>
       <c r="H7" s="9">
         <f>G7-G7/(1+Supuestos!$B$5)</f>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>S (4-8 kg) · Rosa suave · Colgante de cuarzo rosa</t>
+          <t>S (4-8 kg) · Rosa suave · Cuarzo rosa</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1036,13 +1036,13 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>165</v>
+        <v>120</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>18.63</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>44.7</v>
+        <v>36.9</v>
       </c>
       <c r="H8" s="9">
         <f>G8-G8/(1+Supuestos!$B$5)</f>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>S (4-8 kg) · Lavanda · Colgante de amatista</t>
+          <t>S (4-8 kg) · Lavanda · Amatista</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1103,13 +1103,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>165</v>
+        <v>120</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>18.63</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>37.25</v>
+        <v>36.9</v>
       </c>
       <c r="H9" s="9">
         <f>G9-G9/(1+Supuestos!$B$5)</f>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>S (4-8 kg) · Gris roca · Colgante de obsidiana negra</t>
+          <t>S (4-8 kg) · Gris roca · Obsidiana negra</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1170,13 +1170,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>165</v>
+        <v>120</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>18.63</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>37.25</v>
+        <v>36.9</v>
       </c>
       <c r="H10" s="9">
         <f>G10-G10/(1+Supuestos!$B$5)</f>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Correa Elephant Strap</t>
+          <t>Correa Elephant</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2 m · Azul</t>
+          <t>Azul · 2 m</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1243,7 +1243,7 @@
         <v>18.75</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>37.5</v>
+        <v>34.9</v>
       </c>
       <c r="H11" s="9">
         <f>G11-G11/(1+Supuestos!$B$5)</f>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Correa Elephant Strap</t>
+          <t>Correa Elephant</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2 m · Marrón</t>
+          <t>Marrón · 2 m</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1310,7 +1310,7 @@
         <v>18.75</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>37.5</v>
+        <v>34.9</v>
       </c>
       <c r="H12" s="9">
         <f>G12-G12/(1+Supuestos!$B$5)</f>
@@ -1357,12 +1357,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Correa Elephant Strap</t>
+          <t>Correa Elephant</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2 m · Gris</t>
+          <t>Gris · 2 m</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1377,7 +1377,7 @@
         <v>18.75</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>37.5</v>
+        <v>34.9</v>
       </c>
       <c r="H13" s="9">
         <f>G13-G13/(1+Supuestos!$B$5)</f>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3 m · Amarillo</t>
+          <t>Amarillo · 3 m</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1444,7 +1444,7 @@
         <v>15.75</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>31.25</v>
+        <v>29.9</v>
       </c>
       <c r="H14" s="9">
         <f>G14-G14/(1+Supuestos!$B$5)</f>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3 m · Ciruela</t>
+          <t>Ciruela · 3 m</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1511,7 +1511,7 @@
         <v>15.75</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>31.25</v>
+        <v>29.9</v>
       </c>
       <c r="H15" s="9">
         <f>G15-G15/(1+Supuestos!$B$5)</f>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3 m · Durazno</t>
+          <t>Durazno · 3 m</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1578,7 +1578,7 @@
         <v>15.75</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>31.25</v>
+        <v>29.9</v>
       </c>
       <c r="H16" s="9">
         <f>G16-G16/(1+Supuestos!$B$5)</f>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>— · Rosa</t>
+          <t>Rosa · 1,5 m</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1645,7 +1645,7 @@
         <v>12</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>23.13</v>
+        <v>21.9</v>
       </c>
       <c r="H17" s="9">
         <f>G17-G17/(1+Supuestos!$B$5)</f>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>— · Verde</t>
+          <t>Verde · 1,5 m</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1712,7 +1712,7 @@
         <v>12</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>23.13</v>
+        <v>21.9</v>
       </c>
       <c r="H18" s="9">
         <f>G18-G18/(1+Supuestos!$B$5)</f>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>— · Blanco</t>
+          <t>Blanco · 1,5 m</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1779,7 +1779,7 @@
         <v>12</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>23.13</v>
+        <v>21.9</v>
       </c>
       <c r="H19" s="9">
         <f>G19-G19/(1+Supuestos!$B$5)</f>
@@ -1821,17 +1821,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PawB-03</t>
+          <t>PawB-01</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cama acolchada caqui</t>
+          <t>Cama Teddy</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pequeña · Verde caqui</t>
+          <t>Pequeña · 60 × 45 × 17 cm · Peluche marrón</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1840,13 +1840,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1330</v>
+        <v>760</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>19.69</v>
+        <v>16.81</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>41.25</v>
+        <v>34.9</v>
       </c>
       <c r="H20" s="9">
         <f>G20-G20/(1+Supuestos!$B$5)</f>
@@ -1888,17 +1888,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PawB-04</t>
+          <t>PawB-05</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cama acolchada caqui</t>
+          <t>Cama Lucky Elephant</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mediana · Caqui beige</t>
+          <t>60 × 50 × 14 cm · Estampado rojo</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1907,13 +1907,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1600</v>
+        <v>960</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>25.19</v>
+        <v>16.81</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>60.45</v>
+        <v>37.9</v>
       </c>
       <c r="H21" s="9">
         <f>G21-G21/(1+Supuestos!$B$5)</f>
@@ -1955,17 +1955,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PawB-09</t>
+          <t>PawB-06</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cama Corona Real</t>
+          <t>Cama Lucky Elephant</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Mediana · Arena y gris</t>
+          <t>60 × 50 × 14 cm · Estampado verde</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1974,13 +1974,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>840</v>
+        <v>960</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>18</v>
+        <v>16.81</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>37.5</v>
+        <v>37.9</v>
       </c>
       <c r="H22" s="9">
         <f>G22-G22/(1+Supuestos!$B$5)</f>
@@ -2022,17 +2022,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PawB-10</t>
+          <t>PawB-03</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cama Corona Real</t>
+          <t>Cama acolchada caqui</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Grande · Negro y gris</t>
+          <t>Pequeña · 60 × 50 × 15 cm · Verde caqui</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2041,13 +2041,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1000</v>
+        <v>1330</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>21.75</v>
+        <v>19.69</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>45</v>
+        <v>39.9</v>
       </c>
       <c r="H23" s="9">
         <f>G23-G23/(1+Supuestos!$B$5)</f>
@@ -2089,17 +2089,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PawB-05</t>
+          <t>PawB-09</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cama Lucky Elephant</t>
+          <t>Cama Corona Real</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Única · Rojo</t>
+          <t>Mediana · 50 × 50 × 26 cm · Arena y gris</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2108,13 +2108,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>960</v>
+        <v>840</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>16.81</v>
+        <v>18</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>40.35</v>
+        <v>39.9</v>
       </c>
       <c r="H24" s="9">
         <f>G24-G24/(1+Supuestos!$B$5)</f>
@@ -2156,17 +2156,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PawB-06</t>
+          <t>PawB-11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cama Lucky Elephant</t>
+          <t>Cama Patita</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Única · Verde</t>
+          <t>Mediana · 60 cm · Felpa beige</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2175,13 +2175,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>960</v>
+        <v>1000</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>16.81</v>
+        <v>18.13</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>35</v>
+        <v>42.9</v>
       </c>
       <c r="H25" s="9">
         <f>G25-G25/(1+Supuestos!$B$5)</f>
@@ -2223,17 +2223,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PawB-11</t>
+          <t>PawB-02</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cama Patita</t>
+          <t>Cama Teddy</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mediana · Beige</t>
+          <t>Mediana · 70 × 55 × 18 cm · Peluche marrón</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2245,10 +2245,10 @@
         <v>1000</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>18.13</v>
+        <v>21.31</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>40</v>
+        <v>44.9</v>
       </c>
       <c r="H26" s="9">
         <f>G26-G26/(1+Supuestos!$B$5)</f>
@@ -2290,17 +2290,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PawB-12</t>
+          <t>PawB-07</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cama Patita</t>
+          <t>Cama sofá</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Grande · Beige</t>
+          <t>Pequeña · 50 × 50 × 26 cm · Rayas marrones</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1360</v>
+        <v>1250</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>22.63</v>
+        <v>21.75</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>47.5</v>
+        <v>44.9</v>
       </c>
       <c r="H27" s="9">
         <f>G27-G27/(1+Supuestos!$B$5)</f>
@@ -2357,17 +2357,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PawB-07</t>
+          <t>PawB-13</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cama sofá</t>
+          <t>Cama tienda (iglú)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pequeña · Rayas marrones</t>
+          <t>48 × 48 × 40 cm · Verde y naranja</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2376,13 +2376,13 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>21.75</v>
+        <v>20.13</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>45</v>
+        <v>44.9</v>
       </c>
       <c r="H28" s="9">
         <f>G28-G28/(1+Supuestos!$B$5)</f>
@@ -2424,17 +2424,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PawB-08</t>
+          <t>PawB-10</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cama sofá</t>
+          <t>Cama Corona Real</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mediana · Rayas marrones</t>
+          <t>Grande · 50 × 50 × 26 cm · Negro y gris</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2443,13 +2443,13 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1570</v>
+        <v>1000</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>27.44</v>
+        <v>21.75</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>57.5</v>
+        <v>46.9</v>
       </c>
       <c r="H29" s="9">
         <f>G29-G29/(1+Supuestos!$B$5)</f>
@@ -2491,17 +2491,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PawB-01</t>
+          <t>PawB-12</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cama Teddy peluche</t>
+          <t>Cama Patita</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pequeña · Marrón</t>
+          <t>Grande · 70 cm · Felpa beige</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2510,13 +2510,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>760</v>
+        <v>1360</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>16.81</v>
+        <v>22.63</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>35</v>
+        <v>49.9</v>
       </c>
       <c r="H30" s="9">
         <f>G30-G30/(1+Supuestos!$B$5)</f>
@@ -2558,17 +2558,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PawB-02</t>
+          <t>PawB-04</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cama Teddy peluche</t>
+          <t>Cama acolchada caqui</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Mediana · Marrón</t>
+          <t>Mediana · 70 × 60 × 15 cm · Caqui beige</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2577,13 +2577,13 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1000</v>
+        <v>1600</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>21.31</v>
+        <v>25.19</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>45</v>
+        <v>52.9</v>
       </c>
       <c r="H31" s="9">
         <f>G31-G31/(1+Supuestos!$B$5)</f>
@@ -2625,17 +2625,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PawB-13</t>
+          <t>PawB-08</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cama tienda iglú</t>
+          <t>Cama sofá</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>48 × 48 × 40 cm · Verde y naranja</t>
+          <t>Mediana · 60 × 60 × 28 cm · Rayas marrones</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2644,13 +2644,13 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>500</v>
+        <v>1570</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>20.13</v>
+        <v>27.44</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>42.5</v>
+        <v>56.9</v>
       </c>
       <c r="H32" s="9">
         <f>G32-G32/(1+Supuestos!$B$5)</f>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Cama tienda iglú</t>
+          <t>Cama tienda (iglú)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2717,7 +2717,7 @@
         <v>27.44</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>57.5</v>
+        <v>57.9</v>
       </c>
       <c r="H33" s="9">
         <f>G33-G33/(1+Supuestos!$B$5)</f>
@@ -2759,17 +2759,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PAWFB-07</t>
+          <t>PAWFB-09</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Comedero gato con soporte</t>
+          <t>Filtros de repuesto para fuente</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Único · Acero</t>
+          <t>Pack de 4 · compatible con la fuente GRANKHA</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2778,13 +2778,13 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>196</v>
+        <v>160</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>6</v>
+        <v>2.1</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>12.5</v>
+        <v>18.9</v>
       </c>
       <c r="H34" s="9">
         <f>G34-G34/(1+Supuestos!$B$5)</f>
@@ -2826,17 +2826,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PAWFB-01</t>
+          <t>PAWFB-08</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Comedero cobre 18 cm</t>
+          <t>Fuente de agua eléctrica 2,5 L</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>18 cm · Cobre</t>
+          <t>Acero inoxidable 304 · alimentación USB</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2845,13 +2845,13 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103</v>
+        <v>690</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>4.5</v>
+        <v>28.5</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>9.380000000000001</v>
+        <v>49.9</v>
       </c>
       <c r="H35" s="9">
         <f>G35-G35/(1+Supuestos!$B$5)</f>
@@ -2893,17 +2893,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PAWFB-02</t>
+          <t>PAWFB-01</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Comedero cobre 22 cm</t>
+          <t>Comedero estilo cobre</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>22 cm · Cobre</t>
+          <t>Ø 18 cm · Acero inoxidable 304</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2912,13 +2912,13 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>141</v>
+        <v>103</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>11.25</v>
+        <v>13.9</v>
       </c>
       <c r="H36" s="9">
         <f>G36-G36/(1+Supuestos!$B$5)</f>
@@ -2960,17 +2960,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PAWFB-08</t>
+          <t>PAWFB-02</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Fuente de agua eléctrica 2,5 L USB</t>
+          <t>Comedero estilo cobre grande</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2,5 L · Acero</t>
+          <t>Ø 22 cm · Acero inoxidable 304</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2979,13 +2979,13 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>690</v>
+        <v>141</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>28.5</v>
+        <v>5.25</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>61.25</v>
+        <v>16.9</v>
       </c>
       <c r="H37" s="9">
         <f>G37-G37/(1+Supuestos!$B$5)</f>
@@ -3027,17 +3027,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PAWFB-09</t>
+          <t>PAWFB-07</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Filtros de repuesto para fuente (pack 4)</t>
+          <t>Comedero para gatos con soporte</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pack 4 · Blanco</t>
+          <t>Acero inoxidable 304 · cara de gato</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3046,13 +3046,13 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>160</v>
+        <v>196</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>2.1</v>
+        <v>6</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>17.52</v>
+        <v>17.9</v>
       </c>
       <c r="H38" s="9">
         <f>G38-G38/(1+Supuestos!$B$5)</f>
@@ -3099,12 +3099,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Comedero acero + soporte de madera 12 cm</t>
+          <t>Comedero de acero con soporte de madera</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>12 cm · Madera / Acero</t>
+          <t>Ø 12 cm · Acero 201 + madera natural</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3119,7 +3119,7 @@
         <v>10.88</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>22.5</v>
+        <v>26.9</v>
       </c>
       <c r="H39" s="9">
         <f>G39-G39/(1+Supuestos!$B$5)</f>
@@ -3161,17 +3161,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PAWFB-04</t>
+          <t>PAWFB-06</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Comedero doble acero + soporte de madera</t>
+          <t>Comedero de cerámica con soporte de madera</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2 × 12 cm · Madera / Acero</t>
+          <t>Ø 14 cm · Cerámica + madera</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3180,13 +3180,13 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>450</v>
+        <v>799</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>17.25</v>
+        <v>11.25</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>36.25</v>
+        <v>29.9</v>
       </c>
       <c r="H40" s="9">
         <f>G40-G40/(1+Supuestos!$B$5)</f>
@@ -3228,17 +3228,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PAWFB-05</t>
+          <t>PAWFB-04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Comedero doble grande + soporte de madera</t>
+          <t>Comedero doble con soporte de madera</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2 × 13 cm · Madera / Acero</t>
+          <t>2 × 12 cm · Acero 201 + madera</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3247,13 +3247,13 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1020</v>
+        <v>450</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>21</v>
+        <v>17.25</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>47.5</v>
+        <v>39.9</v>
       </c>
       <c r="H41" s="9">
         <f>G41-G41/(1+Supuestos!$B$5)</f>
@@ -3295,17 +3295,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PAWFB-06</t>
+          <t>PAWFB-05</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Comedero cerámica + soporte de madera</t>
+          <t>Comedero doble grande con soporte de madera</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>14 cm · Crema / Madera</t>
+          <t>2 × 13 cm · Acero 201 + madera</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>799</v>
+        <v>1020</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>11.25</v>
+        <v>21</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>23.75</v>
+        <v>44.9</v>
       </c>
       <c r="H42" s="9">
         <f>G42-G42/(1+Supuestos!$B$5)</f>
@@ -3359,30 +3359,432 @@
         <v/>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>PACK-02</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Pack Paseo Guardian XS</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Pack de 2 piezas</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Packs</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>232</v>
+      </c>
+      <c r="F43" s="9" t="n">
+        <v>34.38</v>
+      </c>
+      <c r="G43" s="9" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="H43" s="9">
+        <f>G43-G43/(1+Supuestos!$B$5)</f>
+        <v/>
+      </c>
+      <c r="I43" s="9">
+        <f>G43/(1+Supuestos!$B$5)</f>
+        <v/>
+      </c>
+      <c r="J43" s="9">
+        <f>-G43*Supuestos!$B$6-Supuestos!$B$7</f>
+        <v/>
+      </c>
+      <c r="K43" s="9">
+        <f>-Supuestos!$B$8</f>
+        <v/>
+      </c>
+      <c r="L43" s="9">
+        <f>-Supuestos!$B$9</f>
+        <v/>
+      </c>
+      <c r="M43" s="9">
+        <f>-Supuestos!$B$11*Supuestos!$B$12</f>
+        <v/>
+      </c>
+      <c r="N43" s="9">
+        <f>-I43*Supuestos!$B$10</f>
+        <v/>
+      </c>
+      <c r="O43" s="7">
+        <f>-F43+I43+J43+K43+L43+M43+N43</f>
+        <v/>
+      </c>
+      <c r="P43" s="10">
+        <f>IF(I43=0,0,O43/I43)</f>
+        <v/>
+      </c>
+    </row>
     <row r="44">
-      <c r="N44" s="6" t="inlineStr">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PACK-01</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Pack Paseo Guardian S</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Pack de 2 piezas</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Packs</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>309</v>
+      </c>
+      <c r="F44" s="9" t="n">
+        <v>37.38</v>
+      </c>
+      <c r="G44" s="9" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="H44" s="9">
+        <f>G44-G44/(1+Supuestos!$B$5)</f>
+        <v/>
+      </c>
+      <c r="I44" s="9">
+        <f>G44/(1+Supuestos!$B$5)</f>
+        <v/>
+      </c>
+      <c r="J44" s="9">
+        <f>-G44*Supuestos!$B$6-Supuestos!$B$7</f>
+        <v/>
+      </c>
+      <c r="K44" s="9">
+        <f>-Supuestos!$B$8</f>
+        <v/>
+      </c>
+      <c r="L44" s="9">
+        <f>-Supuestos!$B$9</f>
+        <v/>
+      </c>
+      <c r="M44" s="9">
+        <f>-Supuestos!$B$11*Supuestos!$B$12</f>
+        <v/>
+      </c>
+      <c r="N44" s="9">
+        <f>-I44*Supuestos!$B$10</f>
+        <v/>
+      </c>
+      <c r="O44" s="7">
+        <f>-F44+I44+J44+K44+L44+M44+N44</f>
+        <v/>
+      </c>
+      <c r="P44" s="10">
+        <f>IF(I44=0,0,O44/I44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>PACK-04</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Pack Descanso</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Pack de 2 piezas</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Packs</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1243</v>
+      </c>
+      <c r="F45" s="9" t="n">
+        <v>32.19</v>
+      </c>
+      <c r="G45" s="9" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="H45" s="9">
+        <f>G45-G45/(1+Supuestos!$B$5)</f>
+        <v/>
+      </c>
+      <c r="I45" s="9">
+        <f>G45/(1+Supuestos!$B$5)</f>
+        <v/>
+      </c>
+      <c r="J45" s="9">
+        <f>-G45*Supuestos!$B$6-Supuestos!$B$7</f>
+        <v/>
+      </c>
+      <c r="K45" s="9">
+        <f>-Supuestos!$B$8</f>
+        <v/>
+      </c>
+      <c r="L45" s="9">
+        <f>-Supuestos!$B$9</f>
+        <v/>
+      </c>
+      <c r="M45" s="9">
+        <f>-Supuestos!$B$11*Supuestos!$B$12</f>
+        <v/>
+      </c>
+      <c r="N45" s="9">
+        <f>-I45*Supuestos!$B$10</f>
+        <v/>
+      </c>
+      <c r="O45" s="7">
+        <f>-F45+I45+J45+K45+L45+M45+N45</f>
+        <v/>
+      </c>
+      <c r="P45" s="10">
+        <f>IF(I45=0,0,O45/I45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>PACK-03</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Pack Primeros Días Gato</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Pack de 3 piezas</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Packs</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1046</v>
+      </c>
+      <c r="F46" s="9" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="G46" s="9" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="H46" s="9">
+        <f>G46-G46/(1+Supuestos!$B$5)</f>
+        <v/>
+      </c>
+      <c r="I46" s="9">
+        <f>G46/(1+Supuestos!$B$5)</f>
+        <v/>
+      </c>
+      <c r="J46" s="9">
+        <f>-G46*Supuestos!$B$6-Supuestos!$B$7</f>
+        <v/>
+      </c>
+      <c r="K46" s="9">
+        <f>-Supuestos!$B$8</f>
+        <v/>
+      </c>
+      <c r="L46" s="9">
+        <f>-Supuestos!$B$9</f>
+        <v/>
+      </c>
+      <c r="M46" s="9">
+        <f>-Supuestos!$B$11*Supuestos!$B$12</f>
+        <v/>
+      </c>
+      <c r="N46" s="9">
+        <f>-I46*Supuestos!$B$10</f>
+        <v/>
+      </c>
+      <c r="O46" s="7">
+        <f>-F46+I46+J46+K46+L46+M46+N46</f>
+        <v/>
+      </c>
+      <c r="P46" s="10">
+        <f>IF(I46=0,0,O46/I46)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>PACK-06</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Pack Hidratación</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Pack de 2 piezas</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Packs</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1010</v>
+      </c>
+      <c r="F47" s="9" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="G47" s="9" t="n">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="H47" s="9">
+        <f>G47-G47/(1+Supuestos!$B$5)</f>
+        <v/>
+      </c>
+      <c r="I47" s="9">
+        <f>G47/(1+Supuestos!$B$5)</f>
+        <v/>
+      </c>
+      <c r="J47" s="9">
+        <f>-G47*Supuestos!$B$6-Supuestos!$B$7</f>
+        <v/>
+      </c>
+      <c r="K47" s="9">
+        <f>-Supuestos!$B$8</f>
+        <v/>
+      </c>
+      <c r="L47" s="9">
+        <f>-Supuestos!$B$9</f>
+        <v/>
+      </c>
+      <c r="M47" s="9">
+        <f>-Supuestos!$B$11*Supuestos!$B$12</f>
+        <v/>
+      </c>
+      <c r="N47" s="9">
+        <f>-I47*Supuestos!$B$10</f>
+        <v/>
+      </c>
+      <c r="O47" s="7">
+        <f>-F47+I47+J47+K47+L47+M47+N47</f>
+        <v/>
+      </c>
+      <c r="P47" s="10">
+        <f>IF(I47=0,0,O47/I47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>PACK-05</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Pack Hogar Real</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Pack de 2 piezas</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Packs</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>2020</v>
+      </c>
+      <c r="F48" s="9" t="n">
+        <v>42.75</v>
+      </c>
+      <c r="G48" s="9" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="H48" s="9">
+        <f>G48-G48/(1+Supuestos!$B$5)</f>
+        <v/>
+      </c>
+      <c r="I48" s="9">
+        <f>G48/(1+Supuestos!$B$5)</f>
+        <v/>
+      </c>
+      <c r="J48" s="9">
+        <f>-G48*Supuestos!$B$6-Supuestos!$B$7</f>
+        <v/>
+      </c>
+      <c r="K48" s="9">
+        <f>-Supuestos!$B$8</f>
+        <v/>
+      </c>
+      <c r="L48" s="9">
+        <f>-Supuestos!$B$9</f>
+        <v/>
+      </c>
+      <c r="M48" s="9">
+        <f>-Supuestos!$B$11*Supuestos!$B$12</f>
+        <v/>
+      </c>
+      <c r="N48" s="9">
+        <f>-I48*Supuestos!$B$10</f>
+        <v/>
+      </c>
+      <c r="O48" s="7">
+        <f>-F48+I48+J48+K48+L48+M48+N48</f>
+        <v/>
+      </c>
+      <c r="P48" s="10">
+        <f>IF(I48=0,0,O48/I48)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="N50" s="6" t="inlineStr">
         <is>
           <t>Beneficio medio</t>
         </is>
       </c>
-      <c r="O44" s="9">
-        <f>AVERAGE(O5:O42)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="N45" s="6" t="inlineStr">
+      <c r="O50" s="9">
+        <f>AVERAGE(O5:O48)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="N51" s="6" t="inlineStr">
         <is>
           <t>Margen medio</t>
         </is>
       </c>
-      <c r="O45" s="10">
-        <f>AVERAGE(P5:P42)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="2" t="inlineStr">
+      <c r="O51" s="10">
+        <f>AVERAGE(P5:P48)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>Nota: si un producto tiene beneficio negativo, súbelo de precio o retíralo. Los artículos de bajo importe suelen necesitar venta cruzada (2-3 uds. por pedido) para compensar el coste fijo del envío y de Stripe.</t>
         </is>
@@ -3459,14 +3861,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PAWH-01 · Arnés de paso Guardian · XS (2-4 kg) · Rosa suave · Colgante de cuarzo rosa</t>
+          <t>PAWH-01 · Arnés de paso Guardian · XS (2-4 kg) · Rosa suave · Cuarzo rosa</t>
         </is>
       </c>
       <c r="B5" s="11" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>37.25</v>
+        <v>36.9</v>
       </c>
       <c r="D5" s="9" t="n">
         <v>18.63</v>
@@ -3483,14 +3885,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PawL-01 · Correa Pocket Pod · — · Rosa</t>
+          <t>PawL-01 · Correa Pocket Pod · Rosa · 1,5 m</t>
         </is>
       </c>
       <c r="B6" s="11" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>23.13</v>
+        <v>21.9</v>
       </c>
       <c r="D6" s="9" t="n">
         <v>12</v>
@@ -3507,14 +3909,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PAWFB-01 · Comedero cobre 18 cm · 18 cm · Cobre</t>
+          <t>PAWFB-01 · Comedero estilo cobre · Ø 18 cm · Acero inoxidable 304</t>
         </is>
       </c>
       <c r="B7" s="11" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>9.380000000000001</v>
+        <v>13.9</v>
       </c>
       <c r="D7" s="9" t="n">
         <v>4.5</v>
@@ -3550,7 +3952,7 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>4.95</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="10">
